--- a/assets/libreoffice_calc_njc/77ede3e2-4168-4e30-b390-428f1ebd63e7/EmpBudget_L3_07.xlsx
+++ b/assets/libreoffice_calc_njc/77ede3e2-4168-4e30-b390-428f1ebd63e7/EmpBudget_L3_07.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t xml:space="preserve">David Wu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Garcia</t>
   </si>
 </sst>
 </file>
@@ -295,16 +298,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -343,7 +350,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -792,8 +799,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.56"/>
@@ -851,7 +858,10 @@
       <c r="C4" s="2" t="n">
         <v>66000</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <f aca="false">AVERAGEIF(Employees!$H:$H,"Junior",Employees!$G:$G)</f>
+        <v>3.52</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -871,24 +881,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>62</v>
       </c>
@@ -901,8 +917,12 @@
       <c r="D2" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="0" t="str">
+        <f aca="false">IF(G2&gt;=100000,"Senior",IF(G2&gt;=75000,"Mid","Junior"))</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>54</v>
       </c>
@@ -915,10 +935,28 @@
       <c r="D3" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="H3" s="0" t="str">
+        <f aca="false">IF(G3&gt;=100000,"Senior",IF(G3&gt;=75000,"Mid","Junior"))</f>
+        <v>Junior</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="0" t="str">
+        <f aca="false">IF(G4&gt;=100000,"Senior",IF(G4&gt;=75000,"Mid","Junior"))</f>
+        <v>Junior</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/assets/libreoffice_calc_njc/77ede3e2-4168-4e30-b390-428f1ebd63e7/EmpBudget_L3_07.xlsx
+++ b/assets/libreoffice_calc_njc/77ede3e2-4168-4e30-b390-428f1ebd63e7/EmpBudget_L3_07.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -208,12 +208,6 @@
   </si>
   <si>
     <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Wu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maria Garcia</t>
   </si>
 </sst>
 </file>
@@ -298,20 +292,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -800,7 +790,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.56"/>
@@ -881,32 +871,32 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>23</v>
@@ -937,24 +927,6 @@
       </c>
       <c r="H3" s="0" t="str">
         <f aca="false">IF(G3&gt;=100000,"Senior",IF(G3&gt;=75000,"Mid","Junior"))</f>
-        <v>Junior</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="0" t="str">
-        <f aca="false">IF(G4&gt;=100000,"Senior",IF(G4&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/77ede3e2-4168-4e30-b390-428f1ebd63e7/EmpBudget_L3_07.xlsx
+++ b/assets/libreoffice_calc_njc/77ede3e2-4168-4e30-b390-428f1ebd63e7/EmpBudget_L3_07.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Employees" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="BandSummary" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="LowPerformers" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="cBandSummary" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Employees" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="BandSummary" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="LowPerformers" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -208,6 +209,12 @@
   </si>
   <si>
     <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Wu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Garcia</t>
   </si>
 </sst>
 </file>
@@ -339,6 +346,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
@@ -369,406 +394,406 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1009</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>125000</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>4.9</v>
       </c>
-      <c r="H2" s="0" t="str">
+      <c r="H2" s="1" t="str">
         <f aca="false">IF(E2&gt;=100000,"Senior",IF(E2&gt;=75000,"Mid","Junior"))</f>
         <v>Senior</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>110000</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>4.8</v>
       </c>
-      <c r="H3" s="0" t="str">
+      <c r="H3" s="1" t="str">
         <f aca="false">IF(E3&gt;=100000,"Senior",IF(E3&gt;=75000,"Mid","Junior"))</f>
         <v>Senior</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>95000</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="H4" s="0" t="str">
+      <c r="H4" s="1" t="str">
         <f aca="false">IF(E4&gt;=100000,"Senior",IF(E4&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>1012</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>88000</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>4.3</v>
       </c>
-      <c r="H5" s="0" t="str">
+      <c r="H5" s="1" t="str">
         <f aca="false">IF(E5&gt;=100000,"Senior",IF(E5&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>1007</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>90000</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>4.2</v>
       </c>
-      <c r="H6" s="0" t="str">
+      <c r="H6" s="1" t="str">
         <f aca="false">IF(E6&gt;=100000,"Senior",IF(E6&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>1010</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>115000</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="0" t="n">
+      <c r="G7" s="1" t="n">
         <v>4.1</v>
       </c>
-      <c r="H7" s="0" t="str">
+      <c r="H7" s="1" t="str">
         <f aca="false">IF(E7&gt;=100000,"Senior",IF(E7&gt;=75000,"Mid","Junior"))</f>
         <v>Senior</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>1014</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>78000</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="0" t="str">
+      <c r="H8" s="1" t="str">
         <f aca="false">IF(E8&gt;=100000,"Senior",IF(E8&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>1005</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>72000</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="0" t="str">
+      <c r="H9" s="1" t="str">
         <f aca="false">IF(E9&gt;=100000,"Senior",IF(E9&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>1008</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>62000</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>3.9</v>
       </c>
-      <c r="H10" s="0" t="str">
+      <c r="H10" s="1" t="str">
         <f aca="false">IF(E10&gt;=100000,"Senior",IF(E10&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>1002</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>85000</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>3.8</v>
       </c>
-      <c r="H11" s="0" t="str">
+      <c r="H11" s="1" t="str">
         <f aca="false">IF(E11&gt;=100000,"Senior",IF(E11&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>1013</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>82000</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>3.7</v>
       </c>
-      <c r="H12" s="0" t="str">
+      <c r="H12" s="1" t="str">
         <f aca="false">IF(E12&gt;=100000,"Senior",IF(E12&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>1015</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>76000</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>3.6</v>
       </c>
-      <c r="H13" s="0" t="str">
+      <c r="H13" s="1" t="str">
         <f aca="false">IF(E13&gt;=100000,"Senior",IF(E13&gt;=75000,"Mid","Junior"))</f>
         <v>Mid</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>1006</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>68000</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="H14" s="0" t="str">
+      <c r="H14" s="1" t="str">
         <f aca="false">IF(E14&gt;=100000,"Senior",IF(E14&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>1004</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>65000</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <v>3.2</v>
       </c>
-      <c r="H15" s="0" t="str">
+      <c r="H15" s="1" t="str">
         <f aca="false">IF(E15&gt;=100000,"Senior",IF(E15&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>1011</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>63000</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="0" t="str">
+      <c r="H16" s="1" t="str">
         <f aca="false">IF(E16&gt;=100000,"Senior",IF(E16&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
@@ -784,33 +809,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.56"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E1" s="1" t="e">
+        <f aca="false">IF(#REF!&gt;=100000,"Senior",IF(#REF!&gt;=75000,"Mid","Junior"))</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>59</v>
       </c>
@@ -821,10 +850,11 @@
         <v>116666.67</v>
       </c>
       <c r="D2" s="2" t="n">
+        <f aca="false">AVERAGEIF(Employees!H:H,"Senior",Employees!G:G)</f>
         <v>4.6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>60</v>
       </c>
@@ -835,7 +865,8 @@
         <v>84857.14</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4.01</v>
+        <f aca="false">AVERAGEIF(Employees!H:H,"Mid",Employees!G:G)</f>
+        <v>4.01428571428571</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -849,12 +880,34 @@
         <v>66000</v>
       </c>
       <c r="D4" s="2" t="n">
-        <f aca="false">AVERAGEIF(Employees!$H:$H,"Junior",Employees!$G:$G)</f>
+        <f aca="false">AVERAGEIF(Employees!H:H,"Junior",Employees!G:G)</f>
         <v>3.52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="0" t="e">
+        <f aca="false">AVERAGEIF(E:E,"Junior",#REF!)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="0" t="e">
+        <f aca="false">AVERAGEIF(E:E,"Mid",#REF!)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="0" t="e">
+        <f aca="false">AVERAGEIF(E:E,"Senior",#REF!)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G21" s="0" t="e">
+        <f aca="false">AVERAGEIF(D1:D4,"Senior",C1:C4)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -866,12 +919,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -896,7 +949,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>23</v>
@@ -927,6 +980,24 @@
       </c>
       <c r="H3" s="0" t="str">
         <f aca="false">IF(G3&gt;=100000,"Senior",IF(G3&gt;=75000,"Mid","Junior"))</f>
+        <v>Junior</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="0" t="str">
+        <f aca="false">IF(G4&gt;=100000,"Senior",IF(G4&gt;=75000,"Mid","Junior"))</f>
         <v>Junior</v>
       </c>
     </row>
